--- a/数据表/Datas/__beans__.xlsx
+++ b/数据表/Datas/__beans__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16040"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>全名</t>
     </r>
     <r>
@@ -160,7 +166,7 @@
     <t>status</t>
   </si>
   <si>
-    <t>BattleStatusType</t>
+    <t>BattleStateType</t>
   </si>
   <si>
     <t>附加状态</t>
@@ -510,7 +516,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -550,18 +556,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -869,7 +863,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -935,85 +929,85 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1520,7 +1514,7 @@
     <col min="10" max="10" width="24.75" style="1" customWidth="1"/>
     <col min="11" max="11" width="19" style="1" customWidth="1"/>
     <col min="12" max="12" width="10" style="1" customWidth="1"/>
-    <col min="13" max="13" width="23" style="1" customWidth="1"/>
+    <col min="13" max="13" width="34.3088235294118" style="1" customWidth="1"/>
     <col min="14" max="14" width="10" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>

--- a/数据表/Datas/__beans__.xlsx
+++ b/数据表/Datas/__beans__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -241,39 +241,37 @@
     <t>敌人队伍权重</t>
   </si>
   <si>
-    <t>partyId</t>
-  </si>
-  <si>
-    <r>
-      <t>敌人队伍配置</t>
-    </r>
+    <t>threat</t>
+  </si>
+  <si>
+    <t>EnemyPartyThreatLevel</t>
+  </si>
+  <si>
+    <t>刷新的敌人威胁度</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>刷新权重</t>
+  </si>
+  <si>
+    <t>AlertDistanceBand</t>
+  </si>
+  <si>
+    <t>警惕距离段</t>
+  </si>
+  <si>
+    <t>maxDistanceMilli</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
-      <t>ID</t>
-    </r>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>刷新权重</t>
-  </si>
-  <si>
-    <t>AlertDistanceBand</t>
-  </si>
-  <si>
-    <t>警惕距离段</t>
-  </si>
-  <si>
-    <t>maxDistanceMilli</t>
-  </si>
-  <si>
-    <r>
       <t>该段最大距离，单位千分之一</t>
     </r>
     <r>
@@ -300,6 +298,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>每秒增加警惕值，满值</t>
     </r>
     <r>
@@ -1512,7 +1516,7 @@
     <col min="7" max="7" width="19.6029411764706" style="1" customWidth="1"/>
     <col min="8" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="24.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.625" style="1" customWidth="1"/>
     <col min="12" max="12" width="10" style="1" customWidth="1"/>
     <col min="13" max="13" width="34.3088235294118" style="1" customWidth="1"/>
     <col min="14" max="14" width="10" style="1" customWidth="1"/>
@@ -2033,13 +2037,13 @@
         <v>59</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>22</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N21" s="5"/>
     </row>
@@ -2054,7 +2058,7 @@
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>27</v>
@@ -2063,7 +2067,7 @@
         <v>22</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N22" s="5"/>
     </row>
@@ -2086,21 +2090,21 @@
     <row r="24" customHeight="1" spans="1:14">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>27</v>
@@ -2109,7 +2113,7 @@
         <v>22</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N24" s="5"/>
     </row>
@@ -2124,7 +2128,7 @@
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>27</v>
@@ -2133,7 +2137,7 @@
         <v>22</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N25" s="5"/>
     </row>
